--- a/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67444_completo.xlsx
+++ b/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67444_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4540f34844c84ba8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0eb43e04dc644e66"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.9413</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.5930</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.8170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.1431</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.1438</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7898</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.2282</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.5279</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67444_completo.xlsx
+++ b/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67444_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0eb43e04dc644e66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re0a7571aa1e74796"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,486 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.8007</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.1083</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.2001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.0748</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.9936</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.8149</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.9431</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.6095</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.7955</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.9883</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.1223</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.7981</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.6437</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.7707</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.2711</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.5085</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.8474</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.4636</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.0320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.3793</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.5045</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.3045</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.4229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8643</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.9571</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.1874</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.1002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.8749</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.6880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.8201</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.3562</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -309,7 +789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.1431</x:v>
+        <x:v>     27.8436</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.2282</x:v>
+        <x:v>     29.8516</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.5279</x:v>
+        <x:v>     29.0920</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.6634</x:v>
+        <x:v>     28.3316</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.5214</x:v>
+        <x:v>     37.1935</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.3106</x:v>
+        <x:v>     37.7257</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.9437</x:v>
+        <x:v>     53.9440</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.5924</x:v>
+        <x:v>     45.0372</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.6836</x:v>
+        <x:v>     44.4573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.6383</x:v>
+        <x:v>     46.0021</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.6607</x:v>
+        <x:v>     46.8679</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.1996</x:v>
+        <x:v>     51.0088</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.5915</x:v>
+        <x:v>     61.5918</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.4936</x:v>
+        <x:v>     62.4939</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.8840</x:v>
+        <x:v>     64.8846</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    120.5880</x:v>
+        <x:v>    120.5886</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.2391</x:v>
+        <x:v>     61.2393</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.8178</x:v>
+        <x:v>     62.8188</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.5117</x:v>
+        <x:v>     63.5128</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.4152</x:v>
+        <x:v>     64.4155</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1839,7 +2319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    137.8293</x:v>
+        <x:v>    137.8109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +2364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    119.1247</x:v>
+        <x:v>    119.1167</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1944,7 +2424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    131.1276</x:v>
+        <x:v>    131.1168</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2139,7 +2619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    223.0263</x:v>
+        <x:v>    223.0114</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2229,7 +2709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    832.2625</x:v>
+        <x:v>    103.4976</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2244,7 +2724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>   1329.6088</x:v>
+        <x:v>    112.0634</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2349,7 +2829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    596.1974</x:v>
+        <x:v>    146.4496</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2364,7 +2844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    604.6448</x:v>
+        <x:v>    148.1188</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2379,7 +2859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    328.1234</x:v>
+        <x:v>    155.4384</x:v>
       </x:c>
     </x:row>
     <x:row>
